--- a/results/Backtest_Report.xlsx
+++ b/results/Backtest_Report.xlsx
@@ -696,7 +696,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹104,318.83</t>
+          <t>₹104,318.82</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
         <v>45323</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>98477.17</v>
+        <v>98477.17999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1031,7 +1031,7 @@
         <v>45329</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>99404.31</v>
+        <v>99404.32000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1199,7 +1199,7 @@
         <v>45358</v>
       </c>
       <c r="B48" s="3" t="n">
-        <v>99144.03</v>
+        <v>99144.03999999999</v>
       </c>
     </row>
     <row r="49">
@@ -1207,7 +1207,7 @@
         <v>45362</v>
       </c>
       <c r="B49" s="3" t="n">
-        <v>98692.82000000001</v>
+        <v>98692.81</v>
       </c>
     </row>
     <row r="50">
@@ -1239,7 +1239,7 @@
         <v>45366</v>
       </c>
       <c r="B53" s="3" t="n">
-        <v>97691.96000000001</v>
+        <v>97691.97</v>
       </c>
     </row>
     <row r="54">
@@ -1255,7 +1255,7 @@
         <v>45370</v>
       </c>
       <c r="B55" s="3" t="n">
-        <v>97387.97</v>
+        <v>97387.96000000001</v>
       </c>
     </row>
     <row r="56">
@@ -1279,7 +1279,7 @@
         <v>45373</v>
       </c>
       <c r="B58" s="3" t="n">
-        <v>98504.37</v>
+        <v>98504.38</v>
       </c>
     </row>
     <row r="59">
@@ -1287,7 +1287,7 @@
         <v>45377</v>
       </c>
       <c r="B59" s="3" t="n">
-        <v>98124.2</v>
+        <v>98124.21000000001</v>
       </c>
     </row>
     <row r="60">
@@ -1335,7 +1335,7 @@
         <v>45386</v>
       </c>
       <c r="B65" s="3" t="n">
-        <v>99684.35000000001</v>
+        <v>99684.34</v>
       </c>
     </row>
     <row r="66">
@@ -1343,7 +1343,7 @@
         <v>45387</v>
       </c>
       <c r="B66" s="3" t="n">
-        <v>99715.13</v>
+        <v>99715.12</v>
       </c>
     </row>
     <row r="67">
@@ -1359,7 +1359,7 @@
         <v>45391</v>
       </c>
       <c r="B68" s="3" t="n">
-        <v>99743.09</v>
+        <v>99743.08</v>
       </c>
     </row>
     <row r="69">
@@ -1367,7 +1367,7 @@
         <v>45392</v>
       </c>
       <c r="B69" s="3" t="n">
-        <v>100085.28</v>
+        <v>100085.27</v>
       </c>
     </row>
     <row r="70">
@@ -1375,7 +1375,7 @@
         <v>45394</v>
       </c>
       <c r="B70" s="3" t="n">
-        <v>99690.75</v>
+        <v>99690.74000000001</v>
       </c>
     </row>
     <row r="71">
@@ -1383,7 +1383,7 @@
         <v>45397</v>
       </c>
       <c r="B71" s="3" t="n">
-        <v>99203.14</v>
+        <v>99203.13</v>
       </c>
     </row>
     <row r="72">
@@ -1407,7 +1407,7 @@
         <v>45401</v>
       </c>
       <c r="B74" s="3" t="n">
-        <v>98489.36</v>
+        <v>98489.35000000001</v>
       </c>
     </row>
     <row r="75">
@@ -1447,7 +1447,7 @@
         <v>45408</v>
       </c>
       <c r="B79" s="3" t="n">
-        <v>98859.55</v>
+        <v>98859.53999999999</v>
       </c>
     </row>
     <row r="80">
@@ -1463,7 +1463,7 @@
         <v>45412</v>
       </c>
       <c r="B81" s="3" t="n">
-        <v>98804.21000000001</v>
+        <v>98804.2</v>
       </c>
     </row>
     <row r="82">
@@ -1479,7 +1479,7 @@
         <v>45415</v>
       </c>
       <c r="B83" s="3" t="n">
-        <v>98418.85000000001</v>
+        <v>98418.84</v>
       </c>
     </row>
     <row r="84">
@@ -1695,7 +1695,7 @@
         <v>45455</v>
       </c>
       <c r="B110" s="3" t="n">
-        <v>100611.73</v>
+        <v>100611.72</v>
       </c>
     </row>
     <row r="111">
@@ -1703,7 +1703,7 @@
         <v>45456</v>
       </c>
       <c r="B111" s="3" t="n">
-        <v>100971.93</v>
+        <v>100971.92</v>
       </c>
     </row>
     <row r="112">
@@ -1711,7 +1711,7 @@
         <v>45457</v>
       </c>
       <c r="B112" s="3" t="n">
-        <v>100971.93</v>
+        <v>100971.92</v>
       </c>
     </row>
     <row r="113">
@@ -1719,7 +1719,7 @@
         <v>45461</v>
       </c>
       <c r="B113" s="3" t="n">
-        <v>100971.93</v>
+        <v>100971.92</v>
       </c>
     </row>
     <row r="114">
@@ -1727,7 +1727,7 @@
         <v>45462</v>
       </c>
       <c r="B114" s="3" t="n">
-        <v>100971.93</v>
+        <v>100971.92</v>
       </c>
     </row>
     <row r="115">
@@ -1735,7 +1735,7 @@
         <v>45463</v>
       </c>
       <c r="B115" s="3" t="n">
-        <v>100971.93</v>
+        <v>100971.92</v>
       </c>
     </row>
     <row r="116">
@@ -1743,7 +1743,7 @@
         <v>45464</v>
       </c>
       <c r="B116" s="3" t="n">
-        <v>100971.93</v>
+        <v>100971.92</v>
       </c>
     </row>
     <row r="117">
@@ -1751,7 +1751,7 @@
         <v>45467</v>
       </c>
       <c r="B117" s="3" t="n">
-        <v>100971.93</v>
+        <v>100971.92</v>
       </c>
     </row>
     <row r="118">
@@ -1759,7 +1759,7 @@
         <v>45468</v>
       </c>
       <c r="B118" s="3" t="n">
-        <v>100971.93</v>
+        <v>100971.92</v>
       </c>
     </row>
     <row r="119">
@@ -1767,7 +1767,7 @@
         <v>45469</v>
       </c>
       <c r="B119" s="3" t="n">
-        <v>100971.93</v>
+        <v>100971.92</v>
       </c>
     </row>
     <row r="120">
@@ -1775,7 +1775,7 @@
         <v>45470</v>
       </c>
       <c r="B120" s="3" t="n">
-        <v>100971.93</v>
+        <v>100971.92</v>
       </c>
     </row>
     <row r="121">
@@ -1783,7 +1783,7 @@
         <v>45471</v>
       </c>
       <c r="B121" s="3" t="n">
-        <v>100971.93</v>
+        <v>100971.92</v>
       </c>
     </row>
     <row r="122">
@@ -1791,7 +1791,7 @@
         <v>45474</v>
       </c>
       <c r="B122" s="3" t="n">
-        <v>100971.93</v>
+        <v>100971.92</v>
       </c>
     </row>
     <row r="123">
@@ -1799,7 +1799,7 @@
         <v>45475</v>
       </c>
       <c r="B123" s="3" t="n">
-        <v>100971.93</v>
+        <v>100971.92</v>
       </c>
     </row>
     <row r="124">
@@ -1807,7 +1807,7 @@
         <v>45476</v>
       </c>
       <c r="B124" s="3" t="n">
-        <v>100971.93</v>
+        <v>100971.92</v>
       </c>
     </row>
     <row r="125">
@@ -1815,7 +1815,7 @@
         <v>45477</v>
       </c>
       <c r="B125" s="3" t="n">
-        <v>100971.93</v>
+        <v>100971.92</v>
       </c>
     </row>
     <row r="126">
@@ -1823,7 +1823,7 @@
         <v>45478</v>
       </c>
       <c r="B126" s="3" t="n">
-        <v>100971.93</v>
+        <v>100971.92</v>
       </c>
     </row>
     <row r="127">
@@ -1831,7 +1831,7 @@
         <v>45481</v>
       </c>
       <c r="B127" s="3" t="n">
-        <v>100971.93</v>
+        <v>100971.92</v>
       </c>
     </row>
     <row r="128">
@@ -1839,7 +1839,7 @@
         <v>45482</v>
       </c>
       <c r="B128" s="3" t="n">
-        <v>100971.93</v>
+        <v>100971.92</v>
       </c>
     </row>
     <row r="129">
@@ -1847,7 +1847,7 @@
         <v>45483</v>
       </c>
       <c r="B129" s="3" t="n">
-        <v>100971.93</v>
+        <v>100971.92</v>
       </c>
     </row>
     <row r="130">
@@ -1855,7 +1855,7 @@
         <v>45484</v>
       </c>
       <c r="B130" s="3" t="n">
-        <v>100971.93</v>
+        <v>100971.92</v>
       </c>
     </row>
     <row r="131">
@@ -1863,7 +1863,7 @@
         <v>45485</v>
       </c>
       <c r="B131" s="3" t="n">
-        <v>100971.93</v>
+        <v>100971.92</v>
       </c>
     </row>
     <row r="132">
@@ -1871,7 +1871,7 @@
         <v>45488</v>
       </c>
       <c r="B132" s="3" t="n">
-        <v>100971.93</v>
+        <v>100971.92</v>
       </c>
     </row>
     <row r="133">
@@ -1879,7 +1879,7 @@
         <v>45489</v>
       </c>
       <c r="B133" s="3" t="n">
-        <v>100971.93</v>
+        <v>100971.92</v>
       </c>
     </row>
     <row r="134">
@@ -1887,7 +1887,7 @@
         <v>45491</v>
       </c>
       <c r="B134" s="3" t="n">
-        <v>100971.93</v>
+        <v>100971.92</v>
       </c>
     </row>
     <row r="135">
@@ -1895,7 +1895,7 @@
         <v>45492</v>
       </c>
       <c r="B135" s="3" t="n">
-        <v>100971.93</v>
+        <v>100971.92</v>
       </c>
     </row>
     <row r="136">
@@ -1903,7 +1903,7 @@
         <v>45495</v>
       </c>
       <c r="B136" s="3" t="n">
-        <v>100971.93</v>
+        <v>100971.92</v>
       </c>
     </row>
     <row r="137">
@@ -1911,7 +1911,7 @@
         <v>45496</v>
       </c>
       <c r="B137" s="3" t="n">
-        <v>100971.93</v>
+        <v>100971.92</v>
       </c>
     </row>
     <row r="138">
@@ -1919,7 +1919,7 @@
         <v>45497</v>
       </c>
       <c r="B138" s="3" t="n">
-        <v>100971.93</v>
+        <v>100971.92</v>
       </c>
     </row>
     <row r="139">
@@ -1927,7 +1927,7 @@
         <v>45498</v>
       </c>
       <c r="B139" s="3" t="n">
-        <v>100971.93</v>
+        <v>100971.92</v>
       </c>
     </row>
     <row r="140">
@@ -1935,7 +1935,7 @@
         <v>45499</v>
       </c>
       <c r="B140" s="3" t="n">
-        <v>100971.93</v>
+        <v>100971.92</v>
       </c>
     </row>
     <row r="141">
@@ -1943,7 +1943,7 @@
         <v>45502</v>
       </c>
       <c r="B141" s="3" t="n">
-        <v>100971.93</v>
+        <v>100971.92</v>
       </c>
     </row>
     <row r="142">
@@ -1951,7 +1951,7 @@
         <v>45503</v>
       </c>
       <c r="B142" s="3" t="n">
-        <v>100971.93</v>
+        <v>100971.92</v>
       </c>
     </row>
     <row r="143">
@@ -1959,7 +1959,7 @@
         <v>45504</v>
       </c>
       <c r="B143" s="3" t="n">
-        <v>100971.93</v>
+        <v>100971.92</v>
       </c>
     </row>
     <row r="144">
@@ -1967,7 +1967,7 @@
         <v>45505</v>
       </c>
       <c r="B144" s="3" t="n">
-        <v>100971.93</v>
+        <v>100971.92</v>
       </c>
     </row>
     <row r="145">
@@ -1975,7 +1975,7 @@
         <v>45506</v>
       </c>
       <c r="B145" s="3" t="n">
-        <v>100971.93</v>
+        <v>100971.92</v>
       </c>
     </row>
     <row r="146">
@@ -1983,7 +1983,7 @@
         <v>45509</v>
       </c>
       <c r="B146" s="3" t="n">
-        <v>100971.93</v>
+        <v>100971.92</v>
       </c>
     </row>
     <row r="147">
@@ -2007,7 +2007,7 @@
         <v>45512</v>
       </c>
       <c r="B149" s="3" t="n">
-        <v>101059.18</v>
+        <v>101059.17</v>
       </c>
     </row>
     <row r="150">
@@ -2015,7 +2015,7 @@
         <v>45513</v>
       </c>
       <c r="B150" s="3" t="n">
-        <v>101095.92</v>
+        <v>101095.91</v>
       </c>
     </row>
     <row r="151">
@@ -2023,7 +2023,7 @@
         <v>45516</v>
       </c>
       <c r="B151" s="3" t="n">
-        <v>101268.04</v>
+        <v>101268.03</v>
       </c>
     </row>
     <row r="152">
@@ -2031,7 +2031,7 @@
         <v>45517</v>
       </c>
       <c r="B152" s="3" t="n">
-        <v>101230.5</v>
+        <v>101230.49</v>
       </c>
     </row>
     <row r="153">
@@ -2063,7 +2063,7 @@
         <v>45524</v>
       </c>
       <c r="B156" s="3" t="n">
-        <v>101297.59</v>
+        <v>101297.58</v>
       </c>
     </row>
     <row r="157">
@@ -2095,7 +2095,7 @@
         <v>45530</v>
       </c>
       <c r="B160" s="3" t="n">
-        <v>101315.96</v>
+        <v>101315.95</v>
       </c>
     </row>
     <row r="161">
@@ -2103,7 +2103,7 @@
         <v>45531</v>
       </c>
       <c r="B161" s="3" t="n">
-        <v>101403.42</v>
+        <v>101403.41</v>
       </c>
     </row>
     <row r="162">
@@ -2111,7 +2111,7 @@
         <v>45532</v>
       </c>
       <c r="B162" s="3" t="n">
-        <v>101321.15</v>
+        <v>101321.14</v>
       </c>
     </row>
     <row r="163">
@@ -2423,7 +2423,7 @@
         <v>45588</v>
       </c>
       <c r="B201" s="3" t="n">
-        <v>101410.41</v>
+        <v>101410.4</v>
       </c>
     </row>
     <row r="202">
@@ -2431,7 +2431,7 @@
         <v>45589</v>
       </c>
       <c r="B202" s="3" t="n">
-        <v>100937.89</v>
+        <v>100937.88</v>
       </c>
     </row>
     <row r="203">
@@ -2455,7 +2455,7 @@
         <v>45594</v>
       </c>
       <c r="B205" s="3" t="n">
-        <v>101201.17</v>
+        <v>101201.16</v>
       </c>
     </row>
     <row r="206">
@@ -2471,7 +2471,7 @@
         <v>45596</v>
       </c>
       <c r="B207" s="3" t="n">
-        <v>102431.19</v>
+        <v>102431.18</v>
       </c>
     </row>
     <row r="208">
@@ -2487,7 +2487,7 @@
         <v>45600</v>
       </c>
       <c r="B209" s="3" t="n">
-        <v>102006.63</v>
+        <v>102006.62</v>
       </c>
     </row>
     <row r="210">
@@ -2495,7 +2495,7 @@
         <v>45601</v>
       </c>
       <c r="B210" s="3" t="n">
-        <v>102388.46</v>
+        <v>102388.45</v>
       </c>
     </row>
     <row r="211">
@@ -2503,7 +2503,7 @@
         <v>45602</v>
       </c>
       <c r="B211" s="3" t="n">
-        <v>102863.83</v>
+        <v>102863.82</v>
       </c>
     </row>
     <row r="212">
@@ -2511,7 +2511,7 @@
         <v>45603</v>
       </c>
       <c r="B212" s="3" t="n">
-        <v>102200.85</v>
+        <v>102200.84</v>
       </c>
     </row>
     <row r="213">
@@ -2535,7 +2535,7 @@
         <v>45608</v>
       </c>
       <c r="B215" s="3" t="n">
-        <v>101462.28</v>
+        <v>101462.27</v>
       </c>
     </row>
     <row r="216">
@@ -2671,7 +2671,7 @@
         <v>45635</v>
       </c>
       <c r="B232" s="3" t="n">
-        <v>99609.49000000001</v>
+        <v>99609.48</v>
       </c>
     </row>
     <row r="233">
@@ -2687,7 +2687,7 @@
         <v>45637</v>
       </c>
       <c r="B234" s="3" t="n">
-        <v>100072.45</v>
+        <v>100072.44</v>
       </c>
     </row>
     <row r="235">
@@ -2743,7 +2743,7 @@
         <v>45646</v>
       </c>
       <c r="B241" s="3" t="n">
-        <v>96758.16</v>
+        <v>96758.14999999999</v>
       </c>
     </row>
     <row r="242">
@@ -2767,7 +2767,7 @@
         <v>45652</v>
       </c>
       <c r="B244" s="3" t="n">
-        <v>97059.39999999999</v>
+        <v>97059.39</v>
       </c>
     </row>
     <row r="245">
@@ -2775,7 +2775,7 @@
         <v>45653</v>
       </c>
       <c r="B245" s="3" t="n">
-        <v>97091.02</v>
+        <v>97091.00999999999</v>
       </c>
     </row>
     <row r="246">
@@ -2791,7 +2791,7 @@
         <v>45657</v>
       </c>
       <c r="B247" s="3" t="n">
-        <v>96907.92</v>
+        <v>96907.91</v>
       </c>
     </row>
     <row r="248">
@@ -2807,7 +2807,7 @@
         <v>45659</v>
       </c>
       <c r="B249" s="3" t="n">
-        <v>98288.44</v>
+        <v>98288.42999999999</v>
       </c>
     </row>
     <row r="250">
@@ -2839,7 +2839,7 @@
         <v>45665</v>
       </c>
       <c r="B253" s="3" t="n">
-        <v>98495.10000000001</v>
+        <v>98495.09</v>
       </c>
     </row>
     <row r="254">
@@ -2855,7 +2855,7 @@
         <v>45667</v>
       </c>
       <c r="B255" s="3" t="n">
-        <v>98063.19</v>
+        <v>98063.17999999999</v>
       </c>
     </row>
     <row r="256">
@@ -2871,7 +2871,7 @@
         <v>45671</v>
       </c>
       <c r="B257" s="3" t="n">
-        <v>97748.78</v>
+        <v>97748.77</v>
       </c>
     </row>
     <row r="258">
@@ -2887,7 +2887,7 @@
         <v>45673</v>
       </c>
       <c r="B259" s="3" t="n">
-        <v>98388.14</v>
+        <v>98388.13</v>
       </c>
     </row>
     <row r="260">
@@ -2903,7 +2903,7 @@
         <v>45677</v>
       </c>
       <c r="B261" s="3" t="n">
-        <v>99419.38</v>
+        <v>99419.37</v>
       </c>
     </row>
     <row r="262">
@@ -2911,7 +2911,7 @@
         <v>45678</v>
       </c>
       <c r="B262" s="3" t="n">
-        <v>98796.13</v>
+        <v>98796.12</v>
       </c>
     </row>
     <row r="263">
@@ -2919,7 +2919,7 @@
         <v>45679</v>
       </c>
       <c r="B263" s="3" t="n">
-        <v>98552.16</v>
+        <v>98552.14999999999</v>
       </c>
     </row>
     <row r="264">
@@ -2927,7 +2927,7 @@
         <v>45680</v>
       </c>
       <c r="B264" s="3" t="n">
-        <v>99123.14999999999</v>
+        <v>99123.14</v>
       </c>
     </row>
     <row r="265">
@@ -2951,7 +2951,7 @@
         <v>45685</v>
       </c>
       <c r="B267" s="3" t="n">
-        <v>98042.21000000001</v>
+        <v>98042.2</v>
       </c>
     </row>
     <row r="268">
@@ -2975,7 +2975,7 @@
         <v>45688</v>
       </c>
       <c r="B270" s="3" t="n">
-        <v>100701.29</v>
+        <v>100701.28</v>
       </c>
     </row>
     <row r="271">
@@ -2991,7 +2991,7 @@
         <v>45691</v>
       </c>
       <c r="B272" s="3" t="n">
-        <v>101056.82</v>
+        <v>101056.81</v>
       </c>
     </row>
     <row r="273">
@@ -3023,7 +3023,7 @@
         <v>45695</v>
       </c>
       <c r="B276" s="3" t="n">
-        <v>101638.05</v>
+        <v>101638.04</v>
       </c>
     </row>
     <row r="277">
@@ -3031,7 +3031,7 @@
         <v>45698</v>
       </c>
       <c r="B277" s="3" t="n">
-        <v>101638.05</v>
+        <v>101638.04</v>
       </c>
     </row>
     <row r="278">
@@ -3039,7 +3039,7 @@
         <v>45699</v>
       </c>
       <c r="B278" s="3" t="n">
-        <v>101638.05</v>
+        <v>101638.04</v>
       </c>
     </row>
     <row r="279">
@@ -3047,7 +3047,7 @@
         <v>45700</v>
       </c>
       <c r="B279" s="3" t="n">
-        <v>101638.05</v>
+        <v>101638.04</v>
       </c>
     </row>
     <row r="280">
@@ -3055,7 +3055,7 @@
         <v>45701</v>
       </c>
       <c r="B280" s="3" t="n">
-        <v>101638.05</v>
+        <v>101638.04</v>
       </c>
     </row>
     <row r="281">
@@ -3063,7 +3063,7 @@
         <v>45702</v>
       </c>
       <c r="B281" s="3" t="n">
-        <v>101638.05</v>
+        <v>101638.04</v>
       </c>
     </row>
     <row r="282">
@@ -3071,7 +3071,7 @@
         <v>45705</v>
       </c>
       <c r="B282" s="3" t="n">
-        <v>101638.05</v>
+        <v>101638.04</v>
       </c>
     </row>
     <row r="283">
@@ -3079,7 +3079,7 @@
         <v>45706</v>
       </c>
       <c r="B283" s="3" t="n">
-        <v>101638.05</v>
+        <v>101638.04</v>
       </c>
     </row>
     <row r="284">
@@ -3087,7 +3087,7 @@
         <v>45707</v>
       </c>
       <c r="B284" s="3" t="n">
-        <v>101638.05</v>
+        <v>101638.04</v>
       </c>
     </row>
     <row r="285">
@@ -3095,7 +3095,7 @@
         <v>45708</v>
       </c>
       <c r="B285" s="3" t="n">
-        <v>101638.05</v>
+        <v>101638.04</v>
       </c>
     </row>
     <row r="286">
@@ -3103,7 +3103,7 @@
         <v>45709</v>
       </c>
       <c r="B286" s="3" t="n">
-        <v>101638.05</v>
+        <v>101638.04</v>
       </c>
     </row>
     <row r="287">
@@ -3135,7 +3135,7 @@
         <v>45716</v>
       </c>
       <c r="B290" s="3" t="n">
-        <v>101237.52</v>
+        <v>101237.51</v>
       </c>
     </row>
     <row r="291">
@@ -3143,7 +3143,7 @@
         <v>45719</v>
       </c>
       <c r="B291" s="3" t="n">
-        <v>101362.14</v>
+        <v>101362.13</v>
       </c>
     </row>
     <row r="292">
@@ -3159,7 +3159,7 @@
         <v>45721</v>
       </c>
       <c r="B293" s="3" t="n">
-        <v>102155.47</v>
+        <v>102155.46</v>
       </c>
     </row>
     <row r="294">
@@ -3175,7 +3175,7 @@
         <v>45723</v>
       </c>
       <c r="B295" s="3" t="n">
-        <v>102291.88</v>
+        <v>102291.87</v>
       </c>
     </row>
     <row r="296">
@@ -3191,7 +3191,7 @@
         <v>45727</v>
       </c>
       <c r="B297" s="3" t="n">
-        <v>102155.25</v>
+        <v>102155.24</v>
       </c>
     </row>
     <row r="298">
@@ -3207,7 +3207,7 @@
         <v>45729</v>
       </c>
       <c r="B299" s="3" t="n">
-        <v>101374.46</v>
+        <v>101374.45</v>
       </c>
     </row>
     <row r="300">
@@ -3215,7 +3215,7 @@
         <v>45733</v>
       </c>
       <c r="B300" s="3" t="n">
-        <v>101437.46</v>
+        <v>101437.45</v>
       </c>
     </row>
     <row r="301">
@@ -3223,7 +3223,7 @@
         <v>45734</v>
       </c>
       <c r="B301" s="3" t="n">
-        <v>101437.46</v>
+        <v>101437.45</v>
       </c>
     </row>
     <row r="302">
@@ -3239,7 +3239,7 @@
         <v>45736</v>
       </c>
       <c r="B303" s="3" t="n">
-        <v>102707.34</v>
+        <v>102707.33</v>
       </c>
     </row>
     <row r="304">
@@ -3247,7 +3247,7 @@
         <v>45737</v>
       </c>
       <c r="B304" s="3" t="n">
-        <v>102879.11</v>
+        <v>102879.1</v>
       </c>
     </row>
     <row r="305">
@@ -3255,7 +3255,7 @@
         <v>45740</v>
       </c>
       <c r="B305" s="3" t="n">
-        <v>103352.74</v>
+        <v>103352.73</v>
       </c>
     </row>
     <row r="306">
@@ -3263,7 +3263,7 @@
         <v>45741</v>
       </c>
       <c r="B306" s="3" t="n">
-        <v>103307.01</v>
+        <v>103307</v>
       </c>
     </row>
     <row r="307">
@@ -3271,7 +3271,7 @@
         <v>45742</v>
       </c>
       <c r="B307" s="3" t="n">
-        <v>103177.25</v>
+        <v>103177.24</v>
       </c>
     </row>
     <row r="308">
@@ -3279,7 +3279,7 @@
         <v>45743</v>
       </c>
       <c r="B308" s="3" t="n">
-        <v>103750.01</v>
+        <v>103750</v>
       </c>
     </row>
     <row r="309">
@@ -3303,7 +3303,7 @@
         <v>45749</v>
       </c>
       <c r="B311" s="3" t="n">
-        <v>103062.59</v>
+        <v>103062.58</v>
       </c>
     </row>
     <row r="312">
@@ -3311,7 +3311,7 @@
         <v>45750</v>
       </c>
       <c r="B312" s="3" t="n">
-        <v>101907.07</v>
+        <v>101907.06</v>
       </c>
     </row>
     <row r="313">
@@ -3343,7 +3343,7 @@
         <v>45756</v>
       </c>
       <c r="B316" s="3" t="n">
-        <v>99634.27</v>
+        <v>99634.25999999999</v>
       </c>
     </row>
     <row r="317">
@@ -3351,7 +3351,7 @@
         <v>45758</v>
       </c>
       <c r="B317" s="3" t="n">
-        <v>100450.96</v>
+        <v>100450.95</v>
       </c>
     </row>
     <row r="318">
@@ -3359,7 +3359,7 @@
         <v>45762</v>
       </c>
       <c r="B318" s="3" t="n">
-        <v>101284.13</v>
+        <v>101284.12</v>
       </c>
     </row>
     <row r="319">
@@ -3367,7 +3367,7 @@
         <v>45763</v>
       </c>
       <c r="B319" s="3" t="n">
-        <v>101410.02</v>
+        <v>101410.01</v>
       </c>
     </row>
     <row r="320">
@@ -3375,7 +3375,7 @@
         <v>45764</v>
       </c>
       <c r="B320" s="3" t="n">
-        <v>101467.04</v>
+        <v>101467.03</v>
       </c>
     </row>
     <row r="321">
@@ -3399,7 +3399,7 @@
         <v>45770</v>
       </c>
       <c r="B323" s="3" t="n">
-        <v>102286.75</v>
+        <v>102286.74</v>
       </c>
     </row>
     <row r="324">
@@ -3415,7 +3415,7 @@
         <v>45772</v>
       </c>
       <c r="B325" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="326">
@@ -3423,7 +3423,7 @@
         <v>45775</v>
       </c>
       <c r="B326" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="327">
@@ -3431,7 +3431,7 @@
         <v>45776</v>
       </c>
       <c r="B327" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="328">
@@ -3439,7 +3439,7 @@
         <v>45777</v>
       </c>
       <c r="B328" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="329">
@@ -3447,7 +3447,7 @@
         <v>45779</v>
       </c>
       <c r="B329" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="330">
@@ -3455,7 +3455,7 @@
         <v>45782</v>
       </c>
       <c r="B330" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="331">
@@ -3463,7 +3463,7 @@
         <v>45783</v>
       </c>
       <c r="B331" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="332">
@@ -3471,7 +3471,7 @@
         <v>45784</v>
       </c>
       <c r="B332" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="333">
@@ -3479,7 +3479,7 @@
         <v>45785</v>
       </c>
       <c r="B333" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="334">
@@ -3487,7 +3487,7 @@
         <v>45786</v>
       </c>
       <c r="B334" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="335">
@@ -3495,7 +3495,7 @@
         <v>45789</v>
       </c>
       <c r="B335" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="336">
@@ -3503,7 +3503,7 @@
         <v>45790</v>
       </c>
       <c r="B336" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="337">
@@ -3511,7 +3511,7 @@
         <v>45791</v>
       </c>
       <c r="B337" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="338">
@@ -3519,7 +3519,7 @@
         <v>45792</v>
       </c>
       <c r="B338" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="339">
@@ -3527,7 +3527,7 @@
         <v>45793</v>
       </c>
       <c r="B339" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="340">
@@ -3535,7 +3535,7 @@
         <v>45796</v>
       </c>
       <c r="B340" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="341">
@@ -3543,7 +3543,7 @@
         <v>45797</v>
       </c>
       <c r="B341" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="342">
@@ -3551,7 +3551,7 @@
         <v>45798</v>
       </c>
       <c r="B342" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="343">
@@ -3559,7 +3559,7 @@
         <v>45799</v>
       </c>
       <c r="B343" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="344">
@@ -3567,7 +3567,7 @@
         <v>45800</v>
       </c>
       <c r="B344" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="345">
@@ -3575,7 +3575,7 @@
         <v>45803</v>
       </c>
       <c r="B345" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="346">
@@ -3583,7 +3583,7 @@
         <v>45804</v>
       </c>
       <c r="B346" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="347">
@@ -3591,7 +3591,7 @@
         <v>45805</v>
       </c>
       <c r="B347" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="348">
@@ -3599,7 +3599,7 @@
         <v>45806</v>
       </c>
       <c r="B348" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="349">
@@ -3607,7 +3607,7 @@
         <v>45807</v>
       </c>
       <c r="B349" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="350">
@@ -3615,7 +3615,7 @@
         <v>45810</v>
       </c>
       <c r="B350" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="351">
@@ -3623,7 +3623,7 @@
         <v>45811</v>
       </c>
       <c r="B351" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="352">
@@ -3631,7 +3631,7 @@
         <v>45812</v>
       </c>
       <c r="B352" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="353">
@@ -3639,7 +3639,7 @@
         <v>45813</v>
       </c>
       <c r="B353" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="354">
@@ -3647,7 +3647,7 @@
         <v>45814</v>
       </c>
       <c r="B354" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="355">
@@ -3655,7 +3655,7 @@
         <v>45817</v>
       </c>
       <c r="B355" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="356">
@@ -3663,7 +3663,7 @@
         <v>45818</v>
       </c>
       <c r="B356" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="357">
@@ -3671,7 +3671,7 @@
         <v>45819</v>
       </c>
       <c r="B357" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="358">
@@ -3679,7 +3679,7 @@
         <v>45820</v>
       </c>
       <c r="B358" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="359">
@@ -3687,7 +3687,7 @@
         <v>45821</v>
       </c>
       <c r="B359" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="360">
@@ -3695,7 +3695,7 @@
         <v>45824</v>
       </c>
       <c r="B360" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="361">
@@ -3703,7 +3703,7 @@
         <v>45825</v>
       </c>
       <c r="B361" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="362">
@@ -3711,7 +3711,7 @@
         <v>45826</v>
       </c>
       <c r="B362" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="363">
@@ -3719,7 +3719,7 @@
         <v>45827</v>
       </c>
       <c r="B363" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="364">
@@ -3727,7 +3727,7 @@
         <v>45828</v>
       </c>
       <c r="B364" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="365">
@@ -3735,7 +3735,7 @@
         <v>45831</v>
       </c>
       <c r="B365" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="366">
@@ -3743,7 +3743,7 @@
         <v>45832</v>
       </c>
       <c r="B366" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="367">
@@ -3751,7 +3751,7 @@
         <v>45833</v>
       </c>
       <c r="B367" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="368">
@@ -3759,7 +3759,7 @@
         <v>45834</v>
       </c>
       <c r="B368" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="369">
@@ -3767,7 +3767,7 @@
         <v>45835</v>
       </c>
       <c r="B369" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="370">
@@ -3775,7 +3775,7 @@
         <v>45838</v>
       </c>
       <c r="B370" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="371">
@@ -3783,7 +3783,7 @@
         <v>45839</v>
       </c>
       <c r="B371" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="372">
@@ -3791,7 +3791,7 @@
         <v>45840</v>
       </c>
       <c r="B372" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="373">
@@ -3799,7 +3799,7 @@
         <v>45841</v>
       </c>
       <c r="B373" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="374">
@@ -3807,7 +3807,7 @@
         <v>45842</v>
       </c>
       <c r="B374" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="375">
@@ -3815,7 +3815,7 @@
         <v>45845</v>
       </c>
       <c r="B375" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="376">
@@ -3823,7 +3823,7 @@
         <v>45846</v>
       </c>
       <c r="B376" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="377">
@@ -3831,7 +3831,7 @@
         <v>45847</v>
       </c>
       <c r="B377" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="378">
@@ -3839,7 +3839,7 @@
         <v>45848</v>
       </c>
       <c r="B378" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="379">
@@ -3847,7 +3847,7 @@
         <v>45849</v>
       </c>
       <c r="B379" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="380">
@@ -3855,7 +3855,7 @@
         <v>45852</v>
       </c>
       <c r="B380" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="381">
@@ -3863,7 +3863,7 @@
         <v>45853</v>
       </c>
       <c r="B381" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="382">
@@ -3871,7 +3871,7 @@
         <v>45854</v>
       </c>
       <c r="B382" s="3" t="n">
-        <v>102376.53</v>
+        <v>102376.52</v>
       </c>
     </row>
     <row r="383">
@@ -3895,7 +3895,7 @@
         <v>45859</v>
       </c>
       <c r="B385" s="3" t="n">
-        <v>102342.84</v>
+        <v>102342.83</v>
       </c>
     </row>
     <row r="386">
@@ -3903,7 +3903,7 @@
         <v>45860</v>
       </c>
       <c r="B386" s="3" t="n">
-        <v>102273.36</v>
+        <v>102273.35</v>
       </c>
     </row>
     <row r="387">
@@ -3911,7 +3911,7 @@
         <v>45861</v>
       </c>
       <c r="B387" s="3" t="n">
-        <v>102446.36</v>
+        <v>102446.35</v>
       </c>
     </row>
     <row r="388">
@@ -3919,7 +3919,7 @@
         <v>45862</v>
       </c>
       <c r="B388" s="3" t="n">
-        <v>102139.82</v>
+        <v>102139.81</v>
       </c>
     </row>
     <row r="389">
@@ -3951,7 +3951,7 @@
         <v>45868</v>
       </c>
       <c r="B392" s="3" t="n">
-        <v>101570.92</v>
+        <v>101570.91</v>
       </c>
     </row>
     <row r="393">
@@ -3983,7 +3983,7 @@
         <v>45874</v>
       </c>
       <c r="B396" s="3" t="n">
-        <v>101763.59</v>
+        <v>101763.58</v>
       </c>
     </row>
     <row r="397">
@@ -3991,7 +3991,7 @@
         <v>45875</v>
       </c>
       <c r="B397" s="3" t="n">
-        <v>101374.49</v>
+        <v>101374.48</v>
       </c>
     </row>
     <row r="398">
@@ -3999,7 +3999,7 @@
         <v>45876</v>
       </c>
       <c r="B398" s="3" t="n">
-        <v>101681.85</v>
+        <v>101681.84</v>
       </c>
     </row>
     <row r="399">
@@ -4023,7 +4023,7 @@
         <v>45881</v>
       </c>
       <c r="B401" s="3" t="n">
-        <v>102020.04</v>
+        <v>102020.03</v>
       </c>
     </row>
     <row r="402">
@@ -4063,7 +4063,7 @@
         <v>45889</v>
       </c>
       <c r="B406" s="3" t="n">
-        <v>103287.11</v>
+        <v>103287.1</v>
       </c>
     </row>
     <row r="407">
@@ -4071,7 +4071,7 @@
         <v>45890</v>
       </c>
       <c r="B407" s="3" t="n">
-        <v>103296.85</v>
+        <v>103296.84</v>
       </c>
     </row>
     <row r="408">
@@ -4095,7 +4095,7 @@
         <v>45895</v>
       </c>
       <c r="B410" s="3" t="n">
-        <v>103635.05</v>
+        <v>103635.04</v>
       </c>
     </row>
     <row r="411">
@@ -4103,7 +4103,7 @@
         <v>45897</v>
       </c>
       <c r="B411" s="3" t="n">
-        <v>103221.51</v>
+        <v>103221.5</v>
       </c>
     </row>
     <row r="412">
@@ -4111,7 +4111,7 @@
         <v>45898</v>
       </c>
       <c r="B412" s="3" t="n">
-        <v>103164.03</v>
+        <v>103164.02</v>
       </c>
     </row>
     <row r="413">
@@ -4119,7 +4119,7 @@
         <v>45901</v>
       </c>
       <c r="B413" s="3" t="n">
-        <v>103469.05</v>
+        <v>103469.04</v>
       </c>
     </row>
     <row r="414">
@@ -4127,7 +4127,7 @@
         <v>45902</v>
       </c>
       <c r="B414" s="3" t="n">
-        <v>103402.72</v>
+        <v>103402.71</v>
       </c>
     </row>
     <row r="415">
@@ -4135,7 +4135,7 @@
         <v>45903</v>
       </c>
       <c r="B415" s="3" t="n">
-        <v>103351.2</v>
+        <v>103351.19</v>
       </c>
     </row>
     <row r="416">
@@ -4143,7 +4143,7 @@
         <v>45904</v>
       </c>
       <c r="B416" s="3" t="n">
-        <v>103176.47</v>
+        <v>103176.46</v>
       </c>
     </row>
     <row r="417">
@@ -4159,7 +4159,7 @@
         <v>45908</v>
       </c>
       <c r="B418" s="3" t="n">
-        <v>102770.08</v>
+        <v>102770.07</v>
       </c>
     </row>
     <row r="419">
@@ -4175,7 +4175,7 @@
         <v>45910</v>
       </c>
       <c r="B420" s="3" t="n">
-        <v>103513.07</v>
+        <v>103513.06</v>
       </c>
     </row>
     <row r="421">
@@ -4183,7 +4183,7 @@
         <v>45911</v>
       </c>
       <c r="B421" s="3" t="n">
-        <v>103731.36</v>
+        <v>103731.35</v>
       </c>
     </row>
     <row r="422">
@@ -4191,7 +4191,7 @@
         <v>45912</v>
       </c>
       <c r="B422" s="3" t="n">
-        <v>103906.03</v>
+        <v>103906.02</v>
       </c>
     </row>
     <row r="423">
@@ -4199,7 +4199,7 @@
         <v>45915</v>
       </c>
       <c r="B423" s="3" t="n">
-        <v>103840.08</v>
+        <v>103840.07</v>
       </c>
     </row>
     <row r="424">
@@ -4215,7 +4215,7 @@
         <v>45917</v>
       </c>
       <c r="B425" s="3" t="n">
-        <v>104101.6</v>
+        <v>104101.59</v>
       </c>
     </row>
     <row r="426">
@@ -4239,7 +4239,7 @@
         <v>45922</v>
       </c>
       <c r="B428" s="3" t="n">
-        <v>103577.65</v>
+        <v>103577.64</v>
       </c>
     </row>
     <row r="429">
@@ -4247,7 +4247,7 @@
         <v>45923</v>
       </c>
       <c r="B429" s="3" t="n">
-        <v>103486.84</v>
+        <v>103486.83</v>
       </c>
     </row>
     <row r="430">
@@ -4255,7 +4255,7 @@
         <v>45924</v>
       </c>
       <c r="B430" s="3" t="n">
-        <v>103480.82</v>
+        <v>103480.81</v>
       </c>
     </row>
     <row r="431">
@@ -4279,7 +4279,7 @@
         <v>45929</v>
       </c>
       <c r="B433" s="3" t="n">
-        <v>102932.68</v>
+        <v>102932.67</v>
       </c>
     </row>
     <row r="434">
@@ -4295,7 +4295,7 @@
         <v>45931</v>
       </c>
       <c r="B435" s="3" t="n">
-        <v>103386.7</v>
+        <v>103386.69</v>
       </c>
     </row>
     <row r="436">
@@ -4303,7 +4303,7 @@
         <v>45933</v>
       </c>
       <c r="B436" s="3" t="n">
-        <v>103429.04</v>
+        <v>103429.03</v>
       </c>
     </row>
     <row r="437">
@@ -4319,7 +4319,7 @@
         <v>45937</v>
       </c>
       <c r="B438" s="3" t="n">
-        <v>103575.18</v>
+        <v>103575.17</v>
       </c>
     </row>
     <row r="439">
@@ -4327,7 +4327,7 @@
         <v>45938</v>
       </c>
       <c r="B439" s="3" t="n">
-        <v>104095.56</v>
+        <v>104095.55</v>
       </c>
     </row>
     <row r="440">
@@ -4335,7 +4335,7 @@
         <v>45939</v>
       </c>
       <c r="B440" s="3" t="n">
-        <v>104506.97</v>
+        <v>104506.96</v>
       </c>
     </row>
     <row r="441">
@@ -4351,7 +4351,7 @@
         <v>45943</v>
       </c>
       <c r="B442" s="3" t="n">
-        <v>104413.54</v>
+        <v>104413.53</v>
       </c>
     </row>
     <row r="443">
@@ -4367,7 +4367,7 @@
         <v>45945</v>
       </c>
       <c r="B444" s="3" t="n">
-        <v>104430.82</v>
+        <v>104430.81</v>
       </c>
     </row>
     <row r="445">
@@ -4375,7 +4375,7 @@
         <v>45946</v>
       </c>
       <c r="B445" s="3" t="n">
-        <v>104840.5</v>
+        <v>104840.49</v>
       </c>
     </row>
     <row r="446">
@@ -4391,7 +4391,7 @@
         <v>45950</v>
       </c>
       <c r="B447" s="3" t="n">
-        <v>105060.07</v>
+        <v>105060.06</v>
       </c>
     </row>
     <row r="448">
@@ -4399,7 +4399,7 @@
         <v>45951</v>
       </c>
       <c r="B448" s="3" t="n">
-        <v>105065.2</v>
+        <v>105065.19</v>
       </c>
     </row>
     <row r="449">
@@ -4407,7 +4407,7 @@
         <v>45953</v>
       </c>
       <c r="B449" s="3" t="n">
-        <v>105341.06</v>
+        <v>105341.05</v>
       </c>
     </row>
     <row r="450">
@@ -4423,7 +4423,7 @@
         <v>45957</v>
       </c>
       <c r="B451" s="3" t="n">
-        <v>105509.78</v>
+        <v>105509.77</v>
       </c>
     </row>
     <row r="452">
@@ -4439,7 +4439,7 @@
         <v>45959</v>
       </c>
       <c r="B453" s="3" t="n">
-        <v>105426.94</v>
+        <v>105426.93</v>
       </c>
     </row>
     <row r="454">
@@ -4471,7 +4471,7 @@
         <v>45965</v>
       </c>
       <c r="B457" s="3" t="n">
-        <v>105112.5</v>
+        <v>105112.49</v>
       </c>
     </row>
     <row r="458">
@@ -4487,7 +4487,7 @@
         <v>45968</v>
       </c>
       <c r="B459" s="3" t="n">
-        <v>105031.58</v>
+        <v>105031.57</v>
       </c>
     </row>
     <row r="460">
@@ -4495,7 +4495,7 @@
         <v>45971</v>
       </c>
       <c r="B460" s="3" t="n">
-        <v>104555.02</v>
+        <v>104555.01</v>
       </c>
     </row>
     <row r="461">
@@ -4511,7 +4511,7 @@
         <v>45973</v>
       </c>
       <c r="B462" s="3" t="n">
-        <v>104840.53</v>
+        <v>104840.52</v>
       </c>
     </row>
     <row r="463">
@@ -4519,7 +4519,7 @@
         <v>45974</v>
       </c>
       <c r="B463" s="3" t="n">
-        <v>104641.91</v>
+        <v>104641.9</v>
       </c>
     </row>
     <row r="464">
@@ -4527,7 +4527,7 @@
         <v>45975</v>
       </c>
       <c r="B464" s="3" t="n">
-        <v>104610.65</v>
+        <v>104610.64</v>
       </c>
     </row>
     <row r="465">
@@ -4543,7 +4543,7 @@
         <v>45979</v>
       </c>
       <c r="B466" s="3" t="n">
-        <v>104102.63</v>
+        <v>104102.62</v>
       </c>
     </row>
     <row r="467">
@@ -4551,7 +4551,7 @@
         <v>45980</v>
       </c>
       <c r="B467" s="3" t="n">
-        <v>103815.15</v>
+        <v>103815.14</v>
       </c>
     </row>
     <row r="468">
@@ -4559,7 +4559,7 @@
         <v>45981</v>
       </c>
       <c r="B468" s="3" t="n">
-        <v>103865.07</v>
+        <v>103865.06</v>
       </c>
     </row>
     <row r="469">
@@ -4567,7 +4567,7 @@
         <v>45982</v>
       </c>
       <c r="B469" s="3" t="n">
-        <v>103873.59</v>
+        <v>103873.58</v>
       </c>
     </row>
     <row r="470">
@@ -4591,7 +4591,7 @@
         <v>45987</v>
       </c>
       <c r="B472" s="3" t="n">
-        <v>103551.75</v>
+        <v>103551.74</v>
       </c>
     </row>
     <row r="473">
@@ -4599,7 +4599,7 @@
         <v>45988</v>
       </c>
       <c r="B473" s="3" t="n">
-        <v>103511.48</v>
+        <v>103511.47</v>
       </c>
     </row>
     <row r="474">
@@ -4607,7 +4607,7 @@
         <v>45989</v>
       </c>
       <c r="B474" s="3" t="n">
-        <v>103483.71</v>
+        <v>103483.7</v>
       </c>
     </row>
     <row r="475">
@@ -4615,7 +4615,7 @@
         <v>45992</v>
       </c>
       <c r="B475" s="3" t="n">
-        <v>103678.1</v>
+        <v>103678.09</v>
       </c>
     </row>
     <row r="476">
@@ -4623,7 +4623,7 @@
         <v>45993</v>
       </c>
       <c r="B476" s="3" t="n">
-        <v>103621.17</v>
+        <v>103621.16</v>
       </c>
     </row>
     <row r="477">
@@ -4631,7 +4631,7 @@
         <v>45994</v>
       </c>
       <c r="B477" s="3" t="n">
-        <v>103485.1</v>
+        <v>103485.09</v>
       </c>
     </row>
     <row r="478">
@@ -4647,7 +4647,7 @@
         <v>45996</v>
       </c>
       <c r="B479" s="3" t="n">
-        <v>103394.85</v>
+        <v>103394.84</v>
       </c>
     </row>
     <row r="480">
@@ -4655,7 +4655,7 @@
         <v>45999</v>
       </c>
       <c r="B480" s="3" t="n">
-        <v>103247.67</v>
+        <v>103247.66</v>
       </c>
     </row>
     <row r="481">
@@ -4663,7 +4663,7 @@
         <v>46000</v>
       </c>
       <c r="B481" s="3" t="n">
-        <v>103147.7</v>
+        <v>103147.69</v>
       </c>
     </row>
     <row r="482">
@@ -4679,7 +4679,7 @@
         <v>46002</v>
       </c>
       <c r="B483" s="3" t="n">
-        <v>103236.16</v>
+        <v>103236.15</v>
       </c>
     </row>
     <row r="484">
@@ -4695,7 +4695,7 @@
         <v>46006</v>
       </c>
       <c r="B485" s="3" t="n">
-        <v>103449.67</v>
+        <v>103449.66</v>
       </c>
     </row>
     <row r="486">
@@ -4703,7 +4703,7 @@
         <v>46007</v>
       </c>
       <c r="B486" s="3" t="n">
-        <v>103366.95</v>
+        <v>103366.94</v>
       </c>
     </row>
     <row r="487">
@@ -4727,7 +4727,7 @@
         <v>46010</v>
       </c>
       <c r="B489" s="3" t="n">
-        <v>103435.13</v>
+        <v>103435.12</v>
       </c>
     </row>
     <row r="490">
@@ -4735,7 +4735,7 @@
         <v>46013</v>
       </c>
       <c r="B490" s="3" t="n">
-        <v>103945.8</v>
+        <v>103945.79</v>
       </c>
     </row>
     <row r="491">
@@ -4743,7 +4743,7 @@
         <v>46014</v>
       </c>
       <c r="B491" s="3" t="n">
-        <v>104044.36</v>
+        <v>104044.35</v>
       </c>
     </row>
     <row r="492">
@@ -4767,7 +4767,7 @@
         <v>46020</v>
       </c>
       <c r="B494" s="3" t="n">
-        <v>104117.74</v>
+        <v>104117.73</v>
       </c>
     </row>
     <row r="495">
@@ -4775,7 +4775,7 @@
         <v>46021</v>
       </c>
       <c r="B495" s="3" t="n">
-        <v>104110.95</v>
+        <v>104110.94</v>
       </c>
     </row>
     <row r="496">
@@ -4783,7 +4783,7 @@
         <v>46022</v>
       </c>
       <c r="B496" s="3" t="n">
-        <v>104318.83</v>
+        <v>104318.82</v>
       </c>
     </row>
   </sheetData>
@@ -5417,20 +5417,20 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>45604</v>
+        <v>45587</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>45618</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>5.41</v>
+        <v>5.5</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>340.2</v>
+        <v>411.35</v>
       </c>
       <c r="F23" s="9" t="b">
         <v>1</v>
@@ -5444,20 +5444,20 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>45587</v>
+        <v>45604</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>45618</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>5.5</v>
+        <v>5.41</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>411.35</v>
+        <v>340.2</v>
       </c>
       <c r="F24" s="9" t="b">
         <v>1</v>
@@ -5579,54 +5579,54 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>45609</v>
+        <v>45667</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>45673</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>-10.35</v>
+        <v>5.39</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>-1001.81</v>
-      </c>
-      <c r="F29" s="10" t="b">
-        <v>0</v>
+        <v>524.4400000000001</v>
+      </c>
+      <c r="F29" s="9" t="b">
+        <v>1</v>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>TP</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>45667</v>
+        <v>45609</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>45673</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>5.39</v>
+        <v>-10.35</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>524.4400000000001</v>
-      </c>
-      <c r="F30" s="9" t="b">
-        <v>1</v>
+        <v>-1001.81</v>
+      </c>
+      <c r="F30" s="10" t="b">
+        <v>0</v>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
     </row>
@@ -5781,7 +5781,7 @@
         <v>5.44</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>537.29</v>
+        <v>537.3</v>
       </c>
       <c r="F36" s="9" t="b">
         <v>1</v>
@@ -5916,7 +5916,7 @@
         <v>5.83</v>
       </c>
       <c r="E41" s="8" t="n">
-        <v>579.67</v>
+        <v>579.66</v>
       </c>
       <c r="F41" s="9" t="b">
         <v>1</v>

--- a/results/Backtest_Report.xlsx
+++ b/results/Backtest_Report.xlsx
@@ -860,7 +860,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹105,686.74</t>
+          <t>₹105,686.73</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
         <v>45698</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>100066.98</v>
+        <v>100066.97</v>
       </c>
     </row>
     <row r="32">
@@ -1395,7 +1395,7 @@
         <v>45728</v>
       </c>
       <c r="B52" s="3" t="n">
-        <v>98802.78</v>
+        <v>98802.78999999999</v>
       </c>
     </row>
     <row r="53">
@@ -1443,7 +1443,7 @@
         <v>45737</v>
       </c>
       <c r="B58" s="3" t="n">
-        <v>99964.96000000001</v>
+        <v>99964.95</v>
       </c>
     </row>
     <row r="59">
@@ -1475,7 +1475,7 @@
         <v>45743</v>
       </c>
       <c r="B62" s="3" t="n">
-        <v>100091.73</v>
+        <v>100091.72</v>
       </c>
     </row>
     <row r="63">
@@ -1499,7 +1499,7 @@
         <v>45749</v>
       </c>
       <c r="B65" s="3" t="n">
-        <v>100490.04</v>
+        <v>100490.03</v>
       </c>
     </row>
     <row r="66">
@@ -1523,7 +1523,7 @@
         <v>45754</v>
       </c>
       <c r="B68" s="3" t="n">
-        <v>99113.62</v>
+        <v>99113.61</v>
       </c>
     </row>
     <row r="69">
@@ -1547,7 +1547,7 @@
         <v>45758</v>
       </c>
       <c r="B71" s="3" t="n">
-        <v>100010.8</v>
+        <v>100010.79</v>
       </c>
     </row>
     <row r="72">
@@ -1555,7 +1555,7 @@
         <v>45762</v>
       </c>
       <c r="B72" s="3" t="n">
-        <v>101171.84</v>
+        <v>101171.83</v>
       </c>
     </row>
     <row r="73">
@@ -1627,7 +1627,7 @@
         <v>45776</v>
       </c>
       <c r="B81" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="82">
@@ -1635,7 +1635,7 @@
         <v>45777</v>
       </c>
       <c r="B82" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="83">
@@ -1643,7 +1643,7 @@
         <v>45779</v>
       </c>
       <c r="B83" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="84">
@@ -1651,7 +1651,7 @@
         <v>45782</v>
       </c>
       <c r="B84" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="85">
@@ -1659,7 +1659,7 @@
         <v>45783</v>
       </c>
       <c r="B85" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="86">
@@ -1667,7 +1667,7 @@
         <v>45784</v>
       </c>
       <c r="B86" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="87">
@@ -1675,7 +1675,7 @@
         <v>45785</v>
       </c>
       <c r="B87" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="88">
@@ -1683,7 +1683,7 @@
         <v>45786</v>
       </c>
       <c r="B88" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="89">
@@ -1691,7 +1691,7 @@
         <v>45789</v>
       </c>
       <c r="B89" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="90">
@@ -1699,7 +1699,7 @@
         <v>45790</v>
       </c>
       <c r="B90" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="91">
@@ -1707,7 +1707,7 @@
         <v>45791</v>
       </c>
       <c r="B91" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="92">
@@ -1715,7 +1715,7 @@
         <v>45792</v>
       </c>
       <c r="B92" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="93">
@@ -1723,7 +1723,7 @@
         <v>45793</v>
       </c>
       <c r="B93" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="94">
@@ -1731,7 +1731,7 @@
         <v>45796</v>
       </c>
       <c r="B94" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="95">
@@ -1739,7 +1739,7 @@
         <v>45797</v>
       </c>
       <c r="B95" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="96">
@@ -1747,7 +1747,7 @@
         <v>45798</v>
       </c>
       <c r="B96" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="97">
@@ -1755,7 +1755,7 @@
         <v>45799</v>
       </c>
       <c r="B97" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="98">
@@ -1763,7 +1763,7 @@
         <v>45800</v>
       </c>
       <c r="B98" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="99">
@@ -1771,7 +1771,7 @@
         <v>45803</v>
       </c>
       <c r="B99" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="100">
@@ -1779,7 +1779,7 @@
         <v>45804</v>
       </c>
       <c r="B100" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="101">
@@ -1787,7 +1787,7 @@
         <v>45805</v>
       </c>
       <c r="B101" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="102">
@@ -1795,7 +1795,7 @@
         <v>45806</v>
       </c>
       <c r="B102" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="103">
@@ -1803,7 +1803,7 @@
         <v>45807</v>
       </c>
       <c r="B103" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="104">
@@ -1811,7 +1811,7 @@
         <v>45810</v>
       </c>
       <c r="B104" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="105">
@@ -1819,7 +1819,7 @@
         <v>45811</v>
       </c>
       <c r="B105" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="106">
@@ -1827,7 +1827,7 @@
         <v>45812</v>
       </c>
       <c r="B106" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="107">
@@ -1835,7 +1835,7 @@
         <v>45813</v>
       </c>
       <c r="B107" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="108">
@@ -1843,7 +1843,7 @@
         <v>45814</v>
       </c>
       <c r="B108" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="109">
@@ -1851,7 +1851,7 @@
         <v>45817</v>
       </c>
       <c r="B109" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="110">
@@ -1859,7 +1859,7 @@
         <v>45818</v>
       </c>
       <c r="B110" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="111">
@@ -1867,7 +1867,7 @@
         <v>45819</v>
       </c>
       <c r="B111" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="112">
@@ -1875,7 +1875,7 @@
         <v>45820</v>
       </c>
       <c r="B112" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="113">
@@ -1883,7 +1883,7 @@
         <v>45821</v>
       </c>
       <c r="B113" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="114">
@@ -1891,7 +1891,7 @@
         <v>45824</v>
       </c>
       <c r="B114" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="115">
@@ -1899,7 +1899,7 @@
         <v>45825</v>
       </c>
       <c r="B115" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="116">
@@ -1907,7 +1907,7 @@
         <v>45826</v>
       </c>
       <c r="B116" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="117">
@@ -1915,7 +1915,7 @@
         <v>45827</v>
       </c>
       <c r="B117" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="118">
@@ -1923,7 +1923,7 @@
         <v>45828</v>
       </c>
       <c r="B118" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="119">
@@ -1931,7 +1931,7 @@
         <v>45831</v>
       </c>
       <c r="B119" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="120">
@@ -1939,7 +1939,7 @@
         <v>45832</v>
       </c>
       <c r="B120" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="121">
@@ -1947,7 +1947,7 @@
         <v>45833</v>
       </c>
       <c r="B121" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="122">
@@ -1955,7 +1955,7 @@
         <v>45834</v>
       </c>
       <c r="B122" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="123">
@@ -1963,7 +1963,7 @@
         <v>45835</v>
       </c>
       <c r="B123" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="124">
@@ -1971,7 +1971,7 @@
         <v>45838</v>
       </c>
       <c r="B124" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="125">
@@ -1979,7 +1979,7 @@
         <v>45839</v>
       </c>
       <c r="B125" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="126">
@@ -1987,7 +1987,7 @@
         <v>45840</v>
       </c>
       <c r="B126" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="127">
@@ -1995,7 +1995,7 @@
         <v>45841</v>
       </c>
       <c r="B127" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="128">
@@ -2003,7 +2003,7 @@
         <v>45842</v>
       </c>
       <c r="B128" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="129">
@@ -2011,7 +2011,7 @@
         <v>45845</v>
       </c>
       <c r="B129" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="130">
@@ -2019,7 +2019,7 @@
         <v>45846</v>
       </c>
       <c r="B130" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="131">
@@ -2027,7 +2027,7 @@
         <v>45847</v>
       </c>
       <c r="B131" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="132">
@@ -2035,7 +2035,7 @@
         <v>45848</v>
       </c>
       <c r="B132" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="133">
@@ -2043,7 +2043,7 @@
         <v>45849</v>
       </c>
       <c r="B133" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="134">
@@ -2051,7 +2051,7 @@
         <v>45852</v>
       </c>
       <c r="B134" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="135">
@@ -2059,7 +2059,7 @@
         <v>45853</v>
       </c>
       <c r="B135" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="136">
@@ -2067,7 +2067,7 @@
         <v>45854</v>
       </c>
       <c r="B136" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
     </row>
     <row r="137">
@@ -2083,7 +2083,7 @@
         <v>45856</v>
       </c>
       <c r="B138" s="3" t="n">
-        <v>103822.77</v>
+        <v>103822.76</v>
       </c>
     </row>
     <row r="139">
@@ -2091,7 +2091,7 @@
         <v>45859</v>
       </c>
       <c r="B139" s="3" t="n">
-        <v>103710.75</v>
+        <v>103710.74</v>
       </c>
     </row>
     <row r="140">
@@ -2123,7 +2123,7 @@
         <v>45863</v>
       </c>
       <c r="B143" s="3" t="n">
-        <v>103293.5</v>
+        <v>103293.49</v>
       </c>
     </row>
     <row r="144">
@@ -2139,7 +2139,7 @@
         <v>45867</v>
       </c>
       <c r="B145" s="3" t="n">
-        <v>102776.91</v>
+        <v>102776.9</v>
       </c>
     </row>
     <row r="146">
@@ -2155,7 +2155,7 @@
         <v>45869</v>
       </c>
       <c r="B147" s="3" t="n">
-        <v>102800.39</v>
+        <v>102800.38</v>
       </c>
     </row>
     <row r="148">
@@ -2171,7 +2171,7 @@
         <v>45873</v>
       </c>
       <c r="B149" s="3" t="n">
-        <v>103024.1</v>
+        <v>103024.09</v>
       </c>
     </row>
     <row r="150">
@@ -2187,7 +2187,7 @@
         <v>45875</v>
       </c>
       <c r="B151" s="3" t="n">
-        <v>102742.4</v>
+        <v>102742.39</v>
       </c>
     </row>
     <row r="152">
@@ -2195,7 +2195,7 @@
         <v>45876</v>
       </c>
       <c r="B152" s="3" t="n">
-        <v>103049.76</v>
+        <v>103049.75</v>
       </c>
     </row>
     <row r="153">
@@ -2203,7 +2203,7 @@
         <v>45877</v>
       </c>
       <c r="B153" s="3" t="n">
-        <v>102461.11</v>
+        <v>102461.1</v>
       </c>
     </row>
     <row r="154">
@@ -2259,7 +2259,7 @@
         <v>45889</v>
       </c>
       <c r="B160" s="3" t="n">
-        <v>104655.02</v>
+        <v>104655.01</v>
       </c>
     </row>
     <row r="161">
@@ -2267,7 +2267,7 @@
         <v>45890</v>
       </c>
       <c r="B161" s="3" t="n">
-        <v>104664.76</v>
+        <v>104664.75</v>
       </c>
     </row>
     <row r="162">
@@ -2275,7 +2275,7 @@
         <v>45891</v>
       </c>
       <c r="B162" s="3" t="n">
-        <v>104359.63</v>
+        <v>104359.62</v>
       </c>
     </row>
     <row r="163">
@@ -2291,7 +2291,7 @@
         <v>45895</v>
       </c>
       <c r="B164" s="3" t="n">
-        <v>105002.96</v>
+        <v>105002.95</v>
       </c>
     </row>
     <row r="165">
@@ -2299,7 +2299,7 @@
         <v>45897</v>
       </c>
       <c r="B165" s="3" t="n">
-        <v>104589.42</v>
+        <v>104589.41</v>
       </c>
     </row>
     <row r="166">
@@ -2315,7 +2315,7 @@
         <v>45901</v>
       </c>
       <c r="B167" s="3" t="n">
-        <v>104836.96</v>
+        <v>104836.95</v>
       </c>
     </row>
     <row r="168">
@@ -2323,7 +2323,7 @@
         <v>45902</v>
       </c>
       <c r="B168" s="3" t="n">
-        <v>104770.63</v>
+        <v>104770.62</v>
       </c>
     </row>
     <row r="169">
@@ -2331,7 +2331,7 @@
         <v>45903</v>
       </c>
       <c r="B169" s="3" t="n">
-        <v>104719.11</v>
+        <v>104719.1</v>
       </c>
     </row>
     <row r="170">
@@ -2339,7 +2339,7 @@
         <v>45904</v>
       </c>
       <c r="B170" s="3" t="n">
-        <v>104544.38</v>
+        <v>104544.37</v>
       </c>
     </row>
     <row r="171">
@@ -2347,7 +2347,7 @@
         <v>45905</v>
       </c>
       <c r="B171" s="3" t="n">
-        <v>104317.83</v>
+        <v>104317.82</v>
       </c>
     </row>
     <row r="172">
@@ -2371,7 +2371,7 @@
         <v>45910</v>
       </c>
       <c r="B174" s="3" t="n">
-        <v>104880.98</v>
+        <v>104880.97</v>
       </c>
     </row>
     <row r="175">
@@ -2387,7 +2387,7 @@
         <v>45912</v>
       </c>
       <c r="B176" s="3" t="n">
-        <v>105273.94</v>
+        <v>105273.93</v>
       </c>
     </row>
     <row r="177">
@@ -2411,7 +2411,7 @@
         <v>45917</v>
       </c>
       <c r="B179" s="3" t="n">
-        <v>105469.51</v>
+        <v>105469.5</v>
       </c>
     </row>
     <row r="180">
@@ -2419,7 +2419,7 @@
         <v>45918</v>
       </c>
       <c r="B180" s="3" t="n">
-        <v>105551.35</v>
+        <v>105551.34</v>
       </c>
     </row>
     <row r="181">
@@ -2451,7 +2451,7 @@
         <v>45924</v>
       </c>
       <c r="B184" s="3" t="n">
-        <v>104848.73</v>
+        <v>104848.72</v>
       </c>
     </row>
     <row r="185">
@@ -2459,7 +2459,7 @@
         <v>45925</v>
       </c>
       <c r="B185" s="3" t="n">
-        <v>104508.4</v>
+        <v>104508.39</v>
       </c>
     </row>
     <row r="186">
@@ -2475,7 +2475,7 @@
         <v>45929</v>
       </c>
       <c r="B187" s="3" t="n">
-        <v>104300.59</v>
+        <v>104300.58</v>
       </c>
     </row>
     <row r="188">
@@ -2499,7 +2499,7 @@
         <v>45933</v>
       </c>
       <c r="B190" s="3" t="n">
-        <v>104796.95</v>
+        <v>104796.94</v>
       </c>
     </row>
     <row r="191">
@@ -2531,7 +2531,7 @@
         <v>45939</v>
       </c>
       <c r="B194" s="3" t="n">
-        <v>105874.88</v>
+        <v>105874.87</v>
       </c>
     </row>
     <row r="195">
@@ -2539,7 +2539,7 @@
         <v>45940</v>
       </c>
       <c r="B195" s="3" t="n">
-        <v>105867.45</v>
+        <v>105867.44</v>
       </c>
     </row>
     <row r="196">
@@ -2547,7 +2547,7 @@
         <v>45943</v>
       </c>
       <c r="B196" s="3" t="n">
-        <v>105781.45</v>
+        <v>105781.44</v>
       </c>
     </row>
     <row r="197">
@@ -2555,7 +2555,7 @@
         <v>45944</v>
       </c>
       <c r="B197" s="3" t="n">
-        <v>105540.57</v>
+        <v>105540.56</v>
       </c>
     </row>
     <row r="198">
@@ -2563,7 +2563,7 @@
         <v>45945</v>
       </c>
       <c r="B198" s="3" t="n">
-        <v>105798.73</v>
+        <v>105798.72</v>
       </c>
     </row>
     <row r="199">
@@ -2571,7 +2571,7 @@
         <v>45946</v>
       </c>
       <c r="B199" s="3" t="n">
-        <v>106208.41</v>
+        <v>106208.4</v>
       </c>
     </row>
     <row r="200">
@@ -2611,7 +2611,7 @@
         <v>45954</v>
       </c>
       <c r="B204" s="3" t="n">
-        <v>106629.42</v>
+        <v>106629.41</v>
       </c>
     </row>
     <row r="205">
@@ -2619,7 +2619,7 @@
         <v>45957</v>
       </c>
       <c r="B205" s="3" t="n">
-        <v>106877.69</v>
+        <v>106877.68</v>
       </c>
     </row>
     <row r="206">
@@ -2627,7 +2627,7 @@
         <v>45958</v>
       </c>
       <c r="B206" s="3" t="n">
-        <v>106689.2</v>
+        <v>106689.19</v>
       </c>
     </row>
     <row r="207">
@@ -2635,7 +2635,7 @@
         <v>45959</v>
       </c>
       <c r="B207" s="3" t="n">
-        <v>106794.85</v>
+        <v>106794.84</v>
       </c>
     </row>
     <row r="208">
@@ -2667,7 +2667,7 @@
         <v>45965</v>
       </c>
       <c r="B211" s="3" t="n">
-        <v>106480.41</v>
+        <v>106480.4</v>
       </c>
     </row>
     <row r="212">
@@ -2699,7 +2699,7 @@
         <v>45972</v>
       </c>
       <c r="B215" s="3" t="n">
-        <v>105982.23</v>
+        <v>105982.22</v>
       </c>
     </row>
     <row r="216">
@@ -2715,7 +2715,7 @@
         <v>45974</v>
       </c>
       <c r="B217" s="3" t="n">
-        <v>106009.82</v>
+        <v>106009.81</v>
       </c>
     </row>
     <row r="218">
@@ -2723,7 +2723,7 @@
         <v>45975</v>
       </c>
       <c r="B218" s="3" t="n">
-        <v>105978.56</v>
+        <v>105978.55</v>
       </c>
     </row>
     <row r="219">
@@ -2739,7 +2739,7 @@
         <v>45979</v>
       </c>
       <c r="B220" s="3" t="n">
-        <v>105470.54</v>
+        <v>105470.53</v>
       </c>
     </row>
     <row r="221">
@@ -2747,7 +2747,7 @@
         <v>45980</v>
       </c>
       <c r="B221" s="3" t="n">
-        <v>105183.06</v>
+        <v>105183.05</v>
       </c>
     </row>
     <row r="222">
@@ -2755,7 +2755,7 @@
         <v>45981</v>
       </c>
       <c r="B222" s="3" t="n">
-        <v>105232.98</v>
+        <v>105232.97</v>
       </c>
     </row>
     <row r="223">
@@ -2787,7 +2787,7 @@
         <v>45987</v>
       </c>
       <c r="B226" s="3" t="n">
-        <v>104919.66</v>
+        <v>104919.65</v>
       </c>
     </row>
     <row r="227">
@@ -2811,7 +2811,7 @@
         <v>45992</v>
       </c>
       <c r="B229" s="3" t="n">
-        <v>105046.01</v>
+        <v>105046</v>
       </c>
     </row>
     <row r="230">
@@ -2843,7 +2843,7 @@
         <v>45996</v>
       </c>
       <c r="B233" s="3" t="n">
-        <v>104762.76</v>
+        <v>104762.75</v>
       </c>
     </row>
     <row r="234">
@@ -2859,7 +2859,7 @@
         <v>46000</v>
       </c>
       <c r="B235" s="3" t="n">
-        <v>104515.61</v>
+        <v>104515.6</v>
       </c>
     </row>
     <row r="236">
@@ -2883,7 +2883,7 @@
         <v>46003</v>
       </c>
       <c r="B238" s="3" t="n">
-        <v>104773.28</v>
+        <v>104773.27</v>
       </c>
     </row>
     <row r="239">
@@ -2907,7 +2907,7 @@
         <v>46008</v>
       </c>
       <c r="B241" s="3" t="n">
-        <v>104503.37</v>
+        <v>104503.36</v>
       </c>
     </row>
     <row r="242">
@@ -2923,7 +2923,7 @@
         <v>46010</v>
       </c>
       <c r="B243" s="3" t="n">
-        <v>104803.04</v>
+        <v>104803.03</v>
       </c>
     </row>
     <row r="244">
@@ -2939,7 +2939,7 @@
         <v>46014</v>
       </c>
       <c r="B245" s="3" t="n">
-        <v>105412.27</v>
+        <v>105412.26</v>
       </c>
     </row>
     <row r="246">
@@ -2971,7 +2971,7 @@
         <v>46021</v>
       </c>
       <c r="B249" s="3" t="n">
-        <v>105478.86</v>
+        <v>105478.85</v>
       </c>
     </row>
     <row r="250">
@@ -2979,7 +2979,7 @@
         <v>46022</v>
       </c>
       <c r="B250" s="3" t="n">
-        <v>105686.74</v>
+        <v>105686.73</v>
       </c>
     </row>
   </sheetData>
@@ -4040,7 +4040,7 @@
         <v>45698</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>100066.98</v>
+        <v>100066.97</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>98610.63952246465</v>
@@ -4271,7 +4271,7 @@
         <v>45728</v>
       </c>
       <c r="B52" s="3" t="n">
-        <v>98802.78</v>
+        <v>98802.78999999999</v>
       </c>
       <c r="C52" s="3" t="n">
         <v>94785.19860096453</v>
@@ -4337,7 +4337,7 @@
         <v>45737</v>
       </c>
       <c r="B58" s="3" t="n">
-        <v>99964.96000000001</v>
+        <v>99964.95</v>
       </c>
       <c r="C58" s="3" t="n">
         <v>98305.65907524808</v>
@@ -4381,7 +4381,7 @@
         <v>45743</v>
       </c>
       <c r="B62" s="3" t="n">
-        <v>100091.73</v>
+        <v>100091.72</v>
       </c>
       <c r="C62" s="3" t="n">
         <v>99299.67793320191</v>
@@ -4414,7 +4414,7 @@
         <v>45749</v>
       </c>
       <c r="B65" s="3" t="n">
-        <v>100490.04</v>
+        <v>100490.03</v>
       </c>
       <c r="C65" s="3" t="n">
         <v>98512.7520825642</v>
@@ -4447,7 +4447,7 @@
         <v>45754</v>
       </c>
       <c r="B68" s="3" t="n">
-        <v>99113.62</v>
+        <v>99113.61</v>
       </c>
       <c r="C68" s="3" t="n">
         <v>93791.1854882531</v>
@@ -4480,7 +4480,7 @@
         <v>45758</v>
       </c>
       <c r="B71" s="3" t="n">
-        <v>100010.8</v>
+        <v>100010.79</v>
       </c>
       <c r="C71" s="3" t="n">
         <v>96377.87746156346</v>
@@ -4491,7 +4491,7 @@
         <v>45762</v>
       </c>
       <c r="B72" s="3" t="n">
-        <v>101171.84</v>
+        <v>101171.83</v>
       </c>
       <c r="C72" s="3" t="n">
         <v>98222.82417041859</v>
@@ -4590,7 +4590,7 @@
         <v>45776</v>
       </c>
       <c r="B81" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C81" s="3" t="n">
         <v>102379.610456479</v>
@@ -4601,7 +4601,7 @@
         <v>45777</v>
       </c>
       <c r="B82" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C82" s="3" t="n">
         <v>102409.7270171058</v>
@@ -4612,7 +4612,7 @@
         <v>45779</v>
       </c>
       <c r="B83" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C83" s="3" t="n">
         <v>102326.8921122763</v>
@@ -4623,7 +4623,7 @@
         <v>45782</v>
       </c>
       <c r="B84" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C84" s="3" t="n">
         <v>103313.3847026946</v>
@@ -4634,7 +4634,7 @@
         <v>45783</v>
       </c>
       <c r="B85" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C85" s="3" t="n">
         <v>102639.4103175131</v>
@@ -4645,7 +4645,7 @@
         <v>45784</v>
       </c>
       <c r="B86" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C86" s="3" t="n">
         <v>102710.950075797</v>
@@ -4656,7 +4656,7 @@
         <v>45785</v>
       </c>
       <c r="B87" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C87" s="3" t="n">
         <v>102052.0397161712</v>
@@ -4667,7 +4667,7 @@
         <v>45786</v>
       </c>
       <c r="B88" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C88" s="3" t="n">
         <v>101091.9062978543</v>
@@ -4678,7 +4678,7 @@
         <v>45789</v>
       </c>
       <c r="B89" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C89" s="3" t="n">
         <v>105026.5470415277</v>
@@ -4689,7 +4689,7 @@
         <v>45790</v>
       </c>
       <c r="B90" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C90" s="3" t="n">
         <v>103787.7923480955</v>
@@ -4700,7 +4700,7 @@
         <v>45791</v>
       </c>
       <c r="B91" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C91" s="3" t="n">
         <v>104134.1959929692</v>
@@ -4711,7 +4711,7 @@
         <v>45792</v>
       </c>
       <c r="B92" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>105489.6710308677</v>
@@ -4722,7 +4722,7 @@
         <v>45793</v>
       </c>
       <c r="B93" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C93" s="3" t="n">
         <v>105504.7235659387</v>
@@ -4733,7 +4733,7 @@
         <v>45796</v>
       </c>
       <c r="B94" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C94" s="3" t="n">
         <v>105128.2033604382</v>
@@ -4744,7 +4744,7 @@
         <v>45797</v>
       </c>
       <c r="B95" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C95" s="3" t="n">
         <v>104254.6852164457</v>
@@ -4755,7 +4755,7 @@
         <v>45798</v>
       </c>
       <c r="B96" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C96" s="3" t="n">
         <v>104503.1784404494</v>
@@ -4766,7 +4766,7 @@
         <v>45799</v>
       </c>
       <c r="B97" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C97" s="3" t="n">
         <v>103885.6912784808</v>
@@ -4777,7 +4777,7 @@
         <v>45800</v>
       </c>
       <c r="B98" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C98" s="3" t="n">
         <v>104811.927766676</v>
@@ -4788,7 +4788,7 @@
         <v>45803</v>
       </c>
       <c r="B99" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>105384.245832947</v>
@@ -4799,7 +4799,7 @@
         <v>45804</v>
       </c>
       <c r="B100" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C100" s="3" t="n">
         <v>104766.7471804936</v>
@@ -4810,7 +4810,7 @@
         <v>45805</v>
       </c>
       <c r="B101" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>104555.8967846521</v>
@@ -4821,7 +4821,7 @@
         <v>45806</v>
       </c>
       <c r="B102" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C102" s="3" t="n">
         <v>104875.9412574244</v>
@@ -4832,7 +4832,7 @@
         <v>45807</v>
       </c>
       <c r="B103" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C103" s="3" t="n">
         <v>104661.3219825728</v>
@@ -4843,7 +4843,7 @@
         <v>45810</v>
       </c>
       <c r="B104" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C104" s="3" t="n">
         <v>104522.0113450152</v>
@@ -4854,7 +4854,7 @@
         <v>45811</v>
       </c>
       <c r="B105" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C105" s="3" t="n">
         <v>103832.972934278</v>
@@ -4865,7 +4865,7 @@
         <v>45812</v>
       </c>
       <c r="B106" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>104092.7727953121</v>
@@ -4876,7 +4876,7 @@
         <v>45813</v>
       </c>
       <c r="B107" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C107" s="3" t="n">
         <v>104691.4385431996</v>
@@ -4887,7 +4887,7 @@
         <v>45814</v>
       </c>
       <c r="B108" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C108" s="3" t="n">
         <v>105613.9176428695</v>
@@ -4898,7 +4898,7 @@
         <v>45817</v>
       </c>
       <c r="B109" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C109" s="3" t="n">
         <v>105933.9621156419</v>
@@ -4909,7 +4909,7 @@
         <v>45818</v>
       </c>
       <c r="B110" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C110" s="3" t="n">
         <v>105949.0261411976</v>
@@ -4920,7 +4920,7 @@
         <v>45819</v>
       </c>
       <c r="B111" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>106129.7484859276</v>
@@ -4931,7 +4931,7 @@
         <v>45820</v>
       </c>
       <c r="B112" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C112" s="3" t="n">
         <v>105030.3159205378</v>
@@ -4942,7 +4942,7 @@
         <v>45821</v>
       </c>
       <c r="B113" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C113" s="3" t="n">
         <v>104333.751242265</v>
@@ -4953,7 +4953,7 @@
         <v>45824</v>
       </c>
       <c r="B114" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C114" s="3" t="n">
         <v>105312.7060746631</v>
@@ -4964,7 +4964,7 @@
         <v>45825</v>
       </c>
       <c r="B115" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>104894.7626715056</v>
@@ -4975,7 +4975,7 @@
         <v>45826</v>
       </c>
       <c r="B116" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C116" s="3" t="n">
         <v>104762.9783014834</v>
@@ -4986,7 +4986,7 @@
         <v>45827</v>
       </c>
       <c r="B117" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C117" s="3" t="n">
         <v>104638.7316894816</v>
@@ -4997,7 +4997,7 @@
         <v>45828</v>
       </c>
       <c r="B118" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C118" s="3" t="n">
         <v>105990.4378483699</v>
@@ -5008,7 +5008,7 @@
         <v>45831</v>
       </c>
       <c r="B119" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C119" s="3" t="n">
         <v>105749.459401417</v>
@@ -5019,7 +5019,7 @@
         <v>45832</v>
       </c>
       <c r="B120" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C120" s="3" t="n">
         <v>105964.0786762686</v>
@@ -5030,7 +5030,7 @@
         <v>45833</v>
       </c>
       <c r="B121" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C121" s="3" t="n">
         <v>106709.5928197339</v>
@@ -5041,7 +5041,7 @@
         <v>45834</v>
       </c>
       <c r="B122" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C122" s="3" t="n">
         <v>107831.6271686997</v>
@@ -5052,7 +5052,7 @@
         <v>45835</v>
       </c>
       <c r="B123" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C123" s="3" t="n">
         <v>108422.755158567</v>
@@ -5063,7 +5063,7 @@
         <v>45838</v>
       </c>
       <c r="B124" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C124" s="3" t="n">
         <v>107876.8077548822</v>
@@ -5074,7 +5074,7 @@
         <v>45839</v>
       </c>
       <c r="B125" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>108001.0543668841</v>
@@ -5085,7 +5085,7 @@
         <v>45840</v>
       </c>
       <c r="B126" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C126" s="3" t="n">
         <v>107601.9438682924</v>
@@ -5096,7 +5096,7 @@
         <v>45841</v>
       </c>
       <c r="B127" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C127" s="3" t="n">
         <v>107455.1069631993</v>
@@ -5107,7 +5107,7 @@
         <v>45842</v>
       </c>
       <c r="B128" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C128" s="3" t="n">
         <v>107726.1904802942</v>
@@ -5118,7 +5118,7 @@
         <v>45845</v>
       </c>
       <c r="B129" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C129" s="3" t="n">
         <v>107711.1379452233</v>
@@ -5129,7 +5129,7 @@
         <v>45846</v>
       </c>
       <c r="B130" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C130" s="3" t="n">
         <v>108027.4135389854</v>
@@ -5140,7 +5140,7 @@
         <v>45847</v>
       </c>
       <c r="B131" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C131" s="3" t="n">
         <v>107873.0388758721</v>
@@ -5151,7 +5151,7 @@
         <v>45848</v>
       </c>
       <c r="B132" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C132" s="3" t="n">
         <v>107368.5031793597</v>
@@ -5162,7 +5162,7 @@
         <v>45849</v>
       </c>
       <c r="B133" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C133" s="3" t="n">
         <v>106596.6298637929</v>
@@ -5173,7 +5173,7 @@
         <v>45852</v>
       </c>
       <c r="B134" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>106446.0240796897</v>
@@ -5184,7 +5184,7 @@
         <v>45853</v>
       </c>
       <c r="B135" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>106815.0180176547</v>
@@ -5195,7 +5195,7 @@
         <v>45854</v>
       </c>
       <c r="B136" s="3" t="n">
-        <v>103744.44</v>
+        <v>103744.43</v>
       </c>
       <c r="C136" s="3" t="n">
         <v>106796.1966035736</v>
@@ -5217,7 +5217,7 @@
         <v>45856</v>
       </c>
       <c r="B138" s="3" t="n">
-        <v>103822.77</v>
+        <v>103822.76</v>
       </c>
       <c r="C138" s="3" t="n">
         <v>105964.0786762686</v>
@@ -5228,7 +5228,7 @@
         <v>45859</v>
       </c>
       <c r="B139" s="3" t="n">
-        <v>103710.75</v>
+        <v>103710.74</v>
       </c>
       <c r="C139" s="3" t="n">
         <v>106276.5968815054</v>
@@ -5272,7 +5272,7 @@
         <v>45863</v>
       </c>
       <c r="B143" s="3" t="n">
-        <v>103293.5</v>
+        <v>103293.49</v>
       </c>
       <c r="C143" s="3" t="n">
         <v>105436.9526866649</v>
@@ -5294,7 +5294,7 @@
         <v>45867</v>
       </c>
       <c r="B145" s="3" t="n">
-        <v>102776.91</v>
+        <v>102776.9</v>
       </c>
       <c r="C145" s="3" t="n">
         <v>105459.5429797562</v>
@@ -5316,7 +5316,7 @@
         <v>45869</v>
       </c>
       <c r="B147" s="3" t="n">
-        <v>102800.39</v>
+        <v>102800.38</v>
       </c>
       <c r="C147" s="3" t="n">
         <v>105147.0362650041</v>
@@ -5338,7 +5338,7 @@
         <v>45873</v>
       </c>
       <c r="B149" s="3" t="n">
-        <v>103024.1</v>
+        <v>103024.09</v>
       </c>
       <c r="C149" s="3" t="n">
         <v>104992.6616018908</v>
@@ -5360,7 +5360,7 @@
         <v>45875</v>
       </c>
       <c r="B151" s="3" t="n">
-        <v>102742.4</v>
+        <v>102742.39</v>
       </c>
       <c r="C151" s="3" t="n">
         <v>104412.8172680844</v>
@@ -5371,7 +5371,7 @@
         <v>45876</v>
       </c>
       <c r="B152" s="3" t="n">
-        <v>103049.76</v>
+        <v>103049.75</v>
       </c>
       <c r="C152" s="3" t="n">
         <v>104405.2910005489</v>
@@ -5382,7 +5382,7 @@
         <v>45877</v>
       </c>
       <c r="B153" s="3" t="n">
-        <v>102461.11</v>
+        <v>102461.1</v>
       </c>
       <c r="C153" s="3" t="n">
         <v>103595.7748568199</v>
@@ -5459,7 +5459,7 @@
         <v>45889</v>
       </c>
       <c r="B160" s="3" t="n">
-        <v>104655.02</v>
+        <v>104655.01</v>
       </c>
       <c r="C160" s="3" t="n">
         <v>106374.4843214059</v>
@@ -5470,7 +5470,7 @@
         <v>45890</v>
       </c>
       <c r="B161" s="3" t="n">
-        <v>104664.76</v>
+        <v>104664.75</v>
       </c>
       <c r="C161" s="3" t="n">
         <v>106577.8084497118</v>
@@ -5481,7 +5481,7 @@
         <v>45891</v>
       </c>
       <c r="B162" s="3" t="n">
-        <v>104359.63</v>
+        <v>104359.62</v>
       </c>
       <c r="C162" s="3" t="n">
         <v>105708.0476942446</v>
@@ -5503,7 +5503,7 @@
         <v>45895</v>
       </c>
       <c r="B164" s="3" t="n">
-        <v>105002.96</v>
+        <v>105002.95</v>
       </c>
       <c r="C164" s="3" t="n">
         <v>105067.9587487</v>
@@ -5514,7 +5514,7 @@
         <v>45897</v>
       </c>
       <c r="B165" s="3" t="n">
-        <v>104589.42</v>
+        <v>104589.41</v>
       </c>
       <c r="C165" s="3" t="n">
         <v>104269.7377515167</v>
@@ -5536,7 +5536,7 @@
         <v>45901</v>
       </c>
       <c r="B167" s="3" t="n">
-        <v>104836.96</v>
+        <v>104836.95</v>
       </c>
       <c r="C167" s="3" t="n">
         <v>104740.3880083922</v>
@@ -5547,7 +5547,7 @@
         <v>45902</v>
       </c>
       <c r="B168" s="3" t="n">
-        <v>104770.63</v>
+        <v>104770.62</v>
       </c>
       <c r="C168" s="3" t="n">
         <v>104552.127905642</v>
@@ -5558,7 +5558,7 @@
         <v>45903</v>
       </c>
       <c r="B169" s="3" t="n">
-        <v>104719.11</v>
+        <v>104719.1</v>
       </c>
       <c r="C169" s="3" t="n">
         <v>105026.5470415277</v>
@@ -5569,7 +5569,7 @@
         <v>45904</v>
       </c>
       <c r="B170" s="3" t="n">
-        <v>104544.38</v>
+        <v>104544.37</v>
       </c>
       <c r="C170" s="3" t="n">
         <v>105169.6265580954</v>
@@ -5580,7 +5580,7 @@
         <v>45905</v>
       </c>
       <c r="B171" s="3" t="n">
-        <v>104317.83</v>
+        <v>104317.82</v>
       </c>
       <c r="C171" s="3" t="n">
         <v>105275.0517560161</v>
@@ -5613,7 +5613,7 @@
         <v>45910</v>
       </c>
       <c r="B174" s="3" t="n">
-        <v>104880.98</v>
+        <v>104880.97</v>
       </c>
       <c r="C174" s="3" t="n">
         <v>106118.4533393819</v>
@@ -5635,7 +5635,7 @@
         <v>45912</v>
       </c>
       <c r="B176" s="3" t="n">
-        <v>105273.94</v>
+        <v>105273.93</v>
       </c>
       <c r="C176" s="3" t="n">
         <v>106747.2471383809</v>
@@ -5668,7 +5668,7 @@
         <v>45917</v>
       </c>
       <c r="B179" s="3" t="n">
-        <v>105469.51</v>
+        <v>105469.5</v>
       </c>
       <c r="C179" s="3" t="n">
         <v>107677.2525055864</v>
@@ -5679,7 +5679,7 @@
         <v>45918</v>
       </c>
       <c r="B180" s="3" t="n">
-        <v>105551.35</v>
+        <v>105551.34</v>
       </c>
       <c r="C180" s="3" t="n">
         <v>107948.3475131661</v>
@@ -5723,7 +5723,7 @@
         <v>45924</v>
       </c>
       <c r="B184" s="3" t="n">
-        <v>104848.73</v>
+        <v>104848.72</v>
       </c>
       <c r="C184" s="3" t="n">
         <v>106510.0375704381</v>
@@ -5734,7 +5734,7 @@
         <v>45925</v>
       </c>
       <c r="B185" s="3" t="n">
-        <v>104508.4</v>
+        <v>104508.39</v>
       </c>
       <c r="C185" s="3" t="n">
         <v>105892.5389179847</v>
@@ -5756,7 +5756,7 @@
         <v>45929</v>
       </c>
       <c r="B187" s="3" t="n">
-        <v>104300.59</v>
+        <v>104300.58</v>
       </c>
       <c r="C187" s="3" t="n">
         <v>104875.9412574244</v>
@@ -5789,7 +5789,7 @@
         <v>45933</v>
       </c>
       <c r="B190" s="3" t="n">
-        <v>104796.95</v>
+        <v>104796.94</v>
       </c>
       <c r="C190" s="3" t="n">
         <v>105862.422357358</v>
@@ -5833,7 +5833,7 @@
         <v>45939</v>
       </c>
       <c r="B194" s="3" t="n">
-        <v>105874.88</v>
+        <v>105874.87</v>
       </c>
       <c r="C194" s="3" t="n">
         <v>106950.5597762021</v>
@@ -5844,7 +5844,7 @@
         <v>45940</v>
       </c>
       <c r="B195" s="3" t="n">
-        <v>105867.45</v>
+        <v>105867.44</v>
       </c>
       <c r="C195" s="3" t="n">
         <v>107504.0449379072</v>
@@ -5855,7 +5855,7 @@
         <v>45943</v>
       </c>
       <c r="B196" s="3" t="n">
-        <v>105781.45</v>
+        <v>105781.44</v>
       </c>
       <c r="C196" s="3" t="n">
         <v>107172.716809074</v>
@@ -5866,7 +5866,7 @@
         <v>45944</v>
       </c>
       <c r="B197" s="3" t="n">
-        <v>105540.57</v>
+        <v>105540.56</v>
       </c>
       <c r="C197" s="3" t="n">
         <v>106815.0180176547</v>
@@ -5877,7 +5877,7 @@
         <v>45945</v>
       </c>
       <c r="B198" s="3" t="n">
-        <v>105798.73</v>
+        <v>105798.72</v>
       </c>
       <c r="C198" s="3" t="n">
         <v>107711.1379452233</v>
@@ -5888,7 +5888,7 @@
         <v>45946</v>
       </c>
       <c r="B199" s="3" t="n">
-        <v>106208.41</v>
+        <v>106208.4</v>
       </c>
       <c r="C199" s="3" t="n">
         <v>108701.3879241669</v>
@@ -5943,7 +5943,7 @@
         <v>45954</v>
       </c>
       <c r="B204" s="3" t="n">
-        <v>106629.42</v>
+        <v>106629.41</v>
       </c>
       <c r="C204" s="3" t="n">
         <v>110090.7484017023</v>
@@ -5954,7 +5954,7 @@
         <v>45957</v>
       </c>
       <c r="B205" s="3" t="n">
-        <v>106877.69</v>
+        <v>106877.68</v>
       </c>
       <c r="C205" s="3" t="n">
         <v>110452.2045816469</v>
@@ -5965,7 +5965,7 @@
         <v>45958</v>
       </c>
       <c r="B206" s="3" t="n">
-        <v>106689.2</v>
+        <v>106689.19</v>
       </c>
       <c r="C206" s="3" t="n">
         <v>110358.0745302718</v>
@@ -5976,7 +5976,7 @@
         <v>45959</v>
       </c>
       <c r="B207" s="3" t="n">
-        <v>106794.85</v>
+        <v>106794.84</v>
       </c>
       <c r="C207" s="3" t="n">
         <v>110885.2005198755</v>
@@ -6020,7 +6020,7 @@
         <v>45965</v>
       </c>
       <c r="B211" s="3" t="n">
-        <v>106480.41</v>
+        <v>106480.4</v>
       </c>
       <c r="C211" s="3" t="n">
         <v>109036.4849320102</v>
@@ -6064,7 +6064,7 @@
         <v>45972</v>
       </c>
       <c r="B215" s="3" t="n">
-        <v>105982.23</v>
+        <v>105982.22</v>
       </c>
       <c r="C215" s="3" t="n">
         <v>109499.6089213503</v>
@@ -6086,7 +6086,7 @@
         <v>45974</v>
       </c>
       <c r="B217" s="3" t="n">
-        <v>106009.82</v>
+        <v>106009.81</v>
       </c>
       <c r="C217" s="3" t="n">
         <v>110090.7484017023</v>
@@ -6097,7 +6097,7 @@
         <v>45975</v>
       </c>
       <c r="B218" s="3" t="n">
-        <v>105978.56</v>
+        <v>105978.55</v>
       </c>
       <c r="C218" s="3" t="n">
         <v>110256.4067208765</v>
@@ -6119,7 +6119,7 @@
         <v>45979</v>
       </c>
       <c r="B220" s="3" t="n">
-        <v>105470.54</v>
+        <v>105470.53</v>
       </c>
       <c r="C220" s="3" t="n">
         <v>110309.1250650792</v>
@@ -6130,7 +6130,7 @@
         <v>45980</v>
       </c>
       <c r="B221" s="3" t="n">
-        <v>105183.06</v>
+        <v>105183.05</v>
       </c>
       <c r="C221" s="3" t="n">
         <v>110836.2510546829</v>
@@ -6141,7 +6141,7 @@
         <v>45981</v>
       </c>
       <c r="B222" s="3" t="n">
-        <v>105232.98</v>
+        <v>105232.97</v>
       </c>
       <c r="C222" s="3" t="n">
         <v>111314.4390695787</v>
@@ -6185,7 +6185,7 @@
         <v>45987</v>
       </c>
       <c r="B226" s="3" t="n">
-        <v>104919.66</v>
+        <v>104919.65</v>
       </c>
       <c r="C226" s="3" t="n">
         <v>111453.7497071363</v>
@@ -6218,7 +6218,7 @@
         <v>45992</v>
       </c>
       <c r="B229" s="3" t="n">
-        <v>105046.01</v>
+        <v>105046</v>
       </c>
       <c r="C229" s="3" t="n">
         <v>111487.6351467731</v>
@@ -6262,7 +6262,7 @@
         <v>45996</v>
       </c>
       <c r="B233" s="3" t="n">
-        <v>104762.76</v>
+        <v>104762.75</v>
       </c>
       <c r="C233" s="3" t="n">
         <v>111453.7497071363</v>
@@ -6284,7 +6284,7 @@
         <v>46000</v>
       </c>
       <c r="B235" s="3" t="n">
-        <v>104515.61</v>
+        <v>104515.6</v>
       </c>
       <c r="C235" s="3" t="n">
         <v>110075.6843761465</v>
@@ -6317,7 +6317,7 @@
         <v>46003</v>
       </c>
       <c r="B238" s="3" t="n">
-        <v>104773.28</v>
+        <v>104773.27</v>
       </c>
       <c r="C238" s="3" t="n">
         <v>110956.7402781594</v>
@@ -6350,7 +6350,7 @@
         <v>46008</v>
       </c>
       <c r="B241" s="3" t="n">
-        <v>104503.37</v>
+        <v>104503.36</v>
       </c>
       <c r="C241" s="3" t="n">
         <v>109834.7059291936</v>
@@ -6372,7 +6372,7 @@
         <v>46010</v>
       </c>
       <c r="B243" s="3" t="n">
-        <v>104803.04</v>
+        <v>104803.03</v>
       </c>
       <c r="C243" s="3" t="n">
         <v>110489.6635620526</v>
@@ -6394,7 +6394,7 @@
         <v>46014</v>
       </c>
       <c r="B245" s="3" t="n">
-        <v>105412.27</v>
+        <v>105412.26</v>
       </c>
       <c r="C245" s="3" t="n">
         <v>111329.4916046497</v>
@@ -6438,7 +6438,7 @@
         <v>46021</v>
       </c>
       <c r="B249" s="3" t="n">
-        <v>105478.86</v>
+        <v>105478.85</v>
       </c>
       <c r="C249" s="3" t="n">
         <v>110440.9094351013</v>
@@ -6449,7 +6449,7 @@
         <v>46022</v>
       </c>
       <c r="B250" s="3" t="n">
-        <v>105686.74</v>
+        <v>105686.73</v>
       </c>
       <c r="C250" s="3" t="n">
         <v>111190.1809670921</v>
